--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table82.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table82.xlsx
@@ -79,10 +79,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
-    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.00_-;_-* #,##0.00\-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0.0000_-;_-* #,##0.0000\-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0.000_-;_-* #,##0.000\-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;_-* #,##0.00\-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.0000_-;_-* #,##0.0000\-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.000_-;_-* #,##0.000\-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -215,7 +215,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -226,7 +226,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -235,10 +235,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -247,22 +247,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -754,18 +754,18 @@
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="10" t="s">
+      <c r="D1" s="12"/>
+      <c r="E1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="11"/>
+      <c r="F1" s="12"/>
     </row>
     <row r="2" spans="1:6" ht="29" customHeight="1">
-      <c r="A2" s="12"/>
+      <c r="A2" s="9"/>
       <c r="B2" s="13" t="s">
         <v>3</v>
       </c>
